--- a/LYF_Server/Luaban/MiniTemplate/Datas/#SkillInfo.xlsx
+++ b/LYF_Server/Luaban/MiniTemplate/Datas/#SkillInfo.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\unitypro\LYFMMORGP\LYF_Server\Luaban\MiniTemplate\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\unitypro\Luaban\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12080"/>
+    <workbookView windowWidth="21580" windowHeight="10370"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="60">
   <si>
     <t>##var</t>
   </si>
@@ -96,6 +96,15 @@
     <t>AtkDistance</t>
   </si>
   <si>
+    <t>CanSlideCancel</t>
+  </si>
+  <si>
+    <t>CanJumpCancel</t>
+  </si>
+  <si>
+    <t>CanSkillCancel</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
@@ -150,6 +159,15 @@
     <t>攻击距离</t>
   </si>
   <si>
+    <t>是否可以被滑步打断(1是0否)</t>
+  </si>
+  <si>
+    <t>是否可以被跳跃打断(1是0否)</t>
+  </si>
+  <si>
+    <t>是否可以被其他技能打断(1是0否)</t>
+  </si>
+  <si>
     <t>剑气攻击</t>
   </si>
   <si>
@@ -192,7 +210,8 @@
     <t>Icon/Skill/Skill_330500</t>
   </si>
   <si>
-    <t>无限剑决，剑气凝聚成一并参天巨剑，从天落下。对目标以及周围所有敌人并造成8次&lt;color=#F00&gt;(170-180)%&lt;/color&gt;伤害。</t>
+    <t>无限剑决，剑气凝聚成一并参天巨剑，从天落下。
+对目标以及周围所有敌人并造成8次&lt;color=#F00&gt;(170-180)%&lt;/color&gt;伤害。</t>
   </si>
   <si>
     <t>滑行</t>
@@ -223,7 +242,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -238,6 +257,19 @@
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -384,7 +416,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -393,6 +425,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4874CB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -435,12 +479,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -578,12 +616,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFDEE0E3"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFDEE0E3"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFDEE0E3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFDEE0E3"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -704,58 +757,52 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
@@ -767,89 +814,102 @@
     <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1165,21 +1225,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O10"/>
+  <dimension ref="A1:R200"/>
   <sheetFormatPr defaultColWidth="6.72727272727273" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="2" width="6.72727272727273" style="1" customWidth="1"/>
     <col min="3" max="3" width="10.4545454545455" style="1" customWidth="1"/>
     <col min="4" max="4" width="6.72727272727273" style="1" customWidth="1"/>
-    <col min="5" max="5" width="31.5454545454545" style="1" customWidth="1"/>
-    <col min="6" max="6" width="24.3636363636364" style="1" customWidth="1"/>
+    <col min="5" max="5" width="10.0909090909091" style="1" customWidth="1"/>
+    <col min="6" max="6" width="25.8181818181818" style="1" customWidth="1"/>
     <col min="7" max="7" width="10.9090909090909" style="1" customWidth="1"/>
     <col min="8" max="8" width="6.72727272727273" style="1" customWidth="1"/>
     <col min="9" max="9" width="25.9090909090909" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="6.72727272727273" style="1" customWidth="1"/>
+    <col min="10" max="15" width="6.72727272727273" style="1" customWidth="1"/>
+    <col min="16" max="16" width="12.5454545454545" style="1" customWidth="1"/>
+    <col min="17" max="17" width="11.1818181818182" style="1" customWidth="1"/>
+    <col min="18" max="18" width="13.4545454545455" style="1" customWidth="1"/>
+    <col min="19" max="16384" width="6.72727272727273" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" ht="42" spans="1:18">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1225,100 +1289,127 @@
       <c r="O1" s="2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:15">
+      <c r="P1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" ht="28" spans="1:18">
       <c r="A2" s="2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" ht="28" spans="1:15">
+        <v>19</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="R2" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" ht="112" spans="1:18">
       <c r="A3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B3" s="3"/>
+        <v>22</v>
+      </c>
+      <c r="B3" s="2"/>
       <c r="C3" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
+        <v>35</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q3" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="R3" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" ht="56" spans="1:18">
       <c r="A4" s="4"/>
       <c r="B4" s="4">
         <v>10010</v>
@@ -1327,13 +1418,13 @@
         <v>1</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="E4" s="4">
         <v>1</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="G4" s="4">
         <v>0.5</v>
@@ -1342,7 +1433,7 @@
         <v>1</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="J4" s="4">
         <v>31</v>
@@ -1362,8 +1453,17 @@
       <c r="O4" s="4">
         <v>8</v>
       </c>
-    </row>
-    <row r="5" ht="28" spans="1:15">
+      <c r="P4" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q4" s="5">
+        <v>1</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" ht="56" spans="1:18">
       <c r="A5" s="4"/>
       <c r="B5" s="4">
         <v>10040</v>
@@ -1372,13 +1472,13 @@
         <v>1</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="E5" s="4">
         <v>2</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="G5" s="4">
         <v>8</v>
@@ -1387,7 +1487,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="J5" s="4">
         <v>34</v>
@@ -1395,7 +1495,7 @@
       <c r="K5" s="4">
         <v>130</v>
       </c>
-      <c r="L5" s="4">
+      <c r="L5" s="6">
         <v>4</v>
       </c>
       <c r="M5" s="4">
@@ -1407,8 +1507,17 @@
       <c r="O5" s="4">
         <v>10</v>
       </c>
-    </row>
-    <row r="6" ht="28" spans="1:15">
+      <c r="P5" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="5">
+        <v>0</v>
+      </c>
+      <c r="R5" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" ht="56" spans="1:18">
       <c r="A6" s="4"/>
       <c r="B6" s="4">
         <v>10050</v>
@@ -1417,13 +1526,13 @@
         <v>1</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="E6" s="4">
         <v>2</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="G6" s="4">
         <v>10</v>
@@ -1432,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="J6" s="4">
         <v>35</v>
@@ -1452,8 +1561,17 @@
       <c r="O6" s="4">
         <v>12</v>
       </c>
-    </row>
-    <row r="7" ht="28" spans="1:15">
+      <c r="P6" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="5">
+        <v>0</v>
+      </c>
+      <c r="R6" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" ht="70" spans="1:18">
       <c r="A7" s="4"/>
       <c r="B7" s="4">
         <v>10060</v>
@@ -1462,13 +1580,13 @@
         <v>1</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="E7" s="4">
         <v>2</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="G7" s="4">
         <v>9</v>
@@ -1477,7 +1595,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="J7" s="4">
         <v>36</v>
@@ -1497,8 +1615,17 @@
       <c r="O7" s="4">
         <v>30</v>
       </c>
-    </row>
-    <row r="8" ht="28" spans="1:15">
+      <c r="P7" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="5">
+        <v>0</v>
+      </c>
+      <c r="R7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" ht="70" spans="1:18">
       <c r="A8" s="4"/>
       <c r="B8" s="4">
         <v>10070</v>
@@ -1507,13 +1634,13 @@
         <v>1</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E8" s="4">
         <v>2</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="G8" s="4">
         <v>13</v>
@@ -1522,7 +1649,7 @@
         <v>0</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="J8" s="4">
         <v>37</v>
@@ -1542,8 +1669,17 @@
       <c r="O8" s="4">
         <v>30</v>
       </c>
-    </row>
-    <row r="9" spans="1:15">
+      <c r="P8" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="5">
+        <v>0</v>
+      </c>
+      <c r="R8" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18">
       <c r="A9" s="4"/>
       <c r="B9" s="4">
         <v>10080</v>
@@ -1552,13 +1688,13 @@
         <v>1</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E9" s="4">
         <v>3</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="G9" s="4">
         <v>6</v>
@@ -1567,7 +1703,7 @@
         <v>0</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="J9" s="4">
         <v>41</v>
@@ -1587,8 +1723,17 @@
       <c r="O9" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:15">
+      <c r="P9" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="5">
+        <v>1</v>
+      </c>
+      <c r="R9" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" ht="28" spans="1:18">
       <c r="A10" s="4"/>
       <c r="B10" s="4">
         <v>10090</v>
@@ -1597,13 +1742,13 @@
         <v>1</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="E10" s="4">
         <v>4</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="G10" s="4">
         <v>2</v>
@@ -1612,7 +1757,7 @@
         <v>0</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="J10" s="4">
         <v>51</v>
@@ -1632,6 +1777,965 @@
       <c r="O10" s="4">
         <v>0</v>
       </c>
+      <c r="P10" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="5">
+        <v>0</v>
+      </c>
+      <c r="R10" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18">
+      <c r="P11" s="7"/>
+      <c r="Q11" s="7"/>
+      <c r="R11" s="7"/>
+    </row>
+    <row r="12" spans="1:18">
+      <c r="P12" s="7"/>
+      <c r="Q12" s="7"/>
+      <c r="R12" s="7"/>
+    </row>
+    <row r="13" spans="1:18">
+      <c r="P13" s="7"/>
+      <c r="Q13" s="7"/>
+      <c r="R13" s="7"/>
+    </row>
+    <row r="14" spans="1:18">
+      <c r="P14" s="7"/>
+      <c r="Q14" s="7"/>
+      <c r="R14" s="7"/>
+    </row>
+    <row r="15" spans="1:18">
+      <c r="P15" s="7"/>
+      <c r="Q15" s="7"/>
+      <c r="R15" s="7"/>
+    </row>
+    <row r="16" spans="1:18">
+      <c r="P16" s="7"/>
+      <c r="Q16" s="7"/>
+      <c r="R16" s="7"/>
+    </row>
+    <row r="17" spans="16:18">
+      <c r="P17" s="7"/>
+      <c r="Q17" s="7"/>
+      <c r="R17" s="7"/>
+    </row>
+    <row r="18" spans="16:18">
+      <c r="P18" s="7"/>
+      <c r="Q18" s="7"/>
+      <c r="R18" s="7"/>
+    </row>
+    <row r="19" spans="16:18">
+      <c r="P19" s="7"/>
+      <c r="Q19" s="7"/>
+      <c r="R19" s="7"/>
+    </row>
+    <row r="20" spans="16:18">
+      <c r="P20" s="7"/>
+      <c r="Q20" s="7"/>
+      <c r="R20" s="7"/>
+    </row>
+    <row r="21" spans="16:18">
+      <c r="P21" s="7"/>
+      <c r="Q21" s="7"/>
+      <c r="R21" s="7"/>
+    </row>
+    <row r="22" spans="16:18">
+      <c r="P22" s="7"/>
+      <c r="Q22" s="7"/>
+      <c r="R22" s="7"/>
+    </row>
+    <row r="23" spans="16:18">
+      <c r="P23" s="7"/>
+      <c r="Q23" s="7"/>
+      <c r="R23" s="7"/>
+    </row>
+    <row r="24" spans="16:18">
+      <c r="P24" s="7"/>
+      <c r="Q24" s="7"/>
+      <c r="R24" s="7"/>
+    </row>
+    <row r="25" spans="16:18">
+      <c r="P25" s="7"/>
+      <c r="Q25" s="7"/>
+      <c r="R25" s="7"/>
+    </row>
+    <row r="26" spans="16:18">
+      <c r="P26" s="7"/>
+      <c r="Q26" s="7"/>
+      <c r="R26" s="7"/>
+    </row>
+    <row r="27" spans="16:18">
+      <c r="P27" s="7"/>
+      <c r="Q27" s="7"/>
+      <c r="R27" s="7"/>
+    </row>
+    <row r="28" spans="16:18">
+      <c r="P28" s="7"/>
+      <c r="Q28" s="7"/>
+      <c r="R28" s="7"/>
+    </row>
+    <row r="29" spans="16:18">
+      <c r="P29" s="7"/>
+      <c r="Q29" s="7"/>
+      <c r="R29" s="7"/>
+    </row>
+    <row r="30" spans="16:18">
+      <c r="P30" s="7"/>
+      <c r="Q30" s="7"/>
+      <c r="R30" s="7"/>
+    </row>
+    <row r="31" spans="16:18">
+      <c r="P31" s="7"/>
+      <c r="Q31" s="7"/>
+      <c r="R31" s="7"/>
+    </row>
+    <row r="32" spans="16:18">
+      <c r="P32" s="7"/>
+      <c r="Q32" s="7"/>
+      <c r="R32" s="7"/>
+    </row>
+    <row r="33" spans="16:18">
+      <c r="P33" s="7"/>
+      <c r="Q33" s="7"/>
+      <c r="R33" s="7"/>
+    </row>
+    <row r="34" spans="16:18">
+      <c r="P34" s="7"/>
+      <c r="Q34" s="7"/>
+      <c r="R34" s="7"/>
+    </row>
+    <row r="35" spans="16:18">
+      <c r="P35" s="7"/>
+      <c r="Q35" s="7"/>
+      <c r="R35" s="7"/>
+    </row>
+    <row r="36" spans="16:18">
+      <c r="P36" s="7"/>
+      <c r="Q36" s="7"/>
+      <c r="R36" s="7"/>
+    </row>
+    <row r="37" spans="16:18">
+      <c r="P37" s="7"/>
+      <c r="Q37" s="7"/>
+      <c r="R37" s="7"/>
+    </row>
+    <row r="38" spans="16:18">
+      <c r="P38" s="7"/>
+      <c r="Q38" s="7"/>
+      <c r="R38" s="7"/>
+    </row>
+    <row r="39" spans="16:18">
+      <c r="P39" s="7"/>
+      <c r="Q39" s="7"/>
+      <c r="R39" s="7"/>
+    </row>
+    <row r="40" spans="16:18">
+      <c r="P40" s="7"/>
+      <c r="Q40" s="7"/>
+      <c r="R40" s="7"/>
+    </row>
+    <row r="41" spans="16:18">
+      <c r="P41" s="7"/>
+      <c r="Q41" s="7"/>
+      <c r="R41" s="7"/>
+    </row>
+    <row r="42" spans="16:18">
+      <c r="P42" s="7"/>
+      <c r="Q42" s="7"/>
+      <c r="R42" s="7"/>
+    </row>
+    <row r="43" spans="16:18">
+      <c r="P43" s="7"/>
+      <c r="Q43" s="7"/>
+      <c r="R43" s="7"/>
+    </row>
+    <row r="44" spans="16:18">
+      <c r="P44" s="7"/>
+      <c r="Q44" s="7"/>
+      <c r="R44" s="7"/>
+    </row>
+    <row r="45" spans="16:18">
+      <c r="P45" s="7"/>
+      <c r="Q45" s="7"/>
+      <c r="R45" s="7"/>
+    </row>
+    <row r="46" spans="16:18">
+      <c r="P46" s="7"/>
+      <c r="Q46" s="7"/>
+      <c r="R46" s="7"/>
+    </row>
+    <row r="47" spans="16:18">
+      <c r="P47" s="7"/>
+      <c r="Q47" s="7"/>
+      <c r="R47" s="7"/>
+    </row>
+    <row r="48" spans="16:18">
+      <c r="P48" s="7"/>
+      <c r="Q48" s="7"/>
+      <c r="R48" s="7"/>
+    </row>
+    <row r="49" spans="16:18">
+      <c r="P49" s="7"/>
+      <c r="Q49" s="7"/>
+      <c r="R49" s="7"/>
+    </row>
+    <row r="50" spans="16:18">
+      <c r="P50" s="7"/>
+      <c r="Q50" s="7"/>
+      <c r="R50" s="7"/>
+    </row>
+    <row r="51" spans="16:18">
+      <c r="P51" s="7"/>
+      <c r="Q51" s="7"/>
+      <c r="R51" s="7"/>
+    </row>
+    <row r="52" spans="16:18">
+      <c r="P52" s="7"/>
+      <c r="Q52" s="7"/>
+      <c r="R52" s="7"/>
+    </row>
+    <row r="53" spans="16:18">
+      <c r="P53" s="7"/>
+      <c r="Q53" s="7"/>
+      <c r="R53" s="7"/>
+    </row>
+    <row r="54" spans="16:18">
+      <c r="P54" s="7"/>
+      <c r="Q54" s="7"/>
+      <c r="R54" s="7"/>
+    </row>
+    <row r="55" spans="16:18">
+      <c r="P55" s="7"/>
+      <c r="Q55" s="7"/>
+      <c r="R55" s="7"/>
+    </row>
+    <row r="56" spans="16:18">
+      <c r="P56" s="7"/>
+      <c r="Q56" s="7"/>
+      <c r="R56" s="7"/>
+    </row>
+    <row r="57" spans="16:18">
+      <c r="P57" s="7"/>
+      <c r="Q57" s="7"/>
+      <c r="R57" s="7"/>
+    </row>
+    <row r="58" spans="16:18">
+      <c r="P58" s="7"/>
+      <c r="Q58" s="7"/>
+      <c r="R58" s="7"/>
+    </row>
+    <row r="59" spans="16:18">
+      <c r="P59" s="7"/>
+      <c r="Q59" s="7"/>
+      <c r="R59" s="7"/>
+    </row>
+    <row r="60" spans="16:18">
+      <c r="P60" s="7"/>
+      <c r="Q60" s="7"/>
+      <c r="R60" s="7"/>
+    </row>
+    <row r="61" spans="16:18">
+      <c r="P61" s="7"/>
+      <c r="Q61" s="7"/>
+      <c r="R61" s="7"/>
+    </row>
+    <row r="62" spans="16:18">
+      <c r="P62" s="7"/>
+      <c r="Q62" s="7"/>
+      <c r="R62" s="7"/>
+    </row>
+    <row r="63" spans="16:18">
+      <c r="P63" s="7"/>
+      <c r="Q63" s="7"/>
+      <c r="R63" s="7"/>
+    </row>
+    <row r="64" spans="16:18">
+      <c r="P64" s="7"/>
+      <c r="Q64" s="7"/>
+      <c r="R64" s="7"/>
+    </row>
+    <row r="65" spans="16:18">
+      <c r="P65" s="7"/>
+      <c r="Q65" s="7"/>
+      <c r="R65" s="7"/>
+    </row>
+    <row r="66" spans="16:18">
+      <c r="P66" s="7"/>
+      <c r="Q66" s="7"/>
+      <c r="R66" s="7"/>
+    </row>
+    <row r="67" spans="16:18">
+      <c r="P67" s="7"/>
+      <c r="Q67" s="7"/>
+      <c r="R67" s="7"/>
+    </row>
+    <row r="68" spans="16:18">
+      <c r="P68" s="7"/>
+      <c r="Q68" s="7"/>
+      <c r="R68" s="7"/>
+    </row>
+    <row r="69" spans="16:18">
+      <c r="P69" s="7"/>
+      <c r="Q69" s="7"/>
+      <c r="R69" s="7"/>
+    </row>
+    <row r="70" spans="16:18">
+      <c r="P70" s="7"/>
+      <c r="Q70" s="7"/>
+      <c r="R70" s="7"/>
+    </row>
+    <row r="71" spans="16:18">
+      <c r="P71" s="7"/>
+      <c r="Q71" s="7"/>
+      <c r="R71" s="7"/>
+    </row>
+    <row r="72" spans="16:18">
+      <c r="P72" s="7"/>
+      <c r="Q72" s="7"/>
+      <c r="R72" s="7"/>
+    </row>
+    <row r="73" spans="16:18">
+      <c r="P73" s="7"/>
+      <c r="Q73" s="7"/>
+      <c r="R73" s="7"/>
+    </row>
+    <row r="74" spans="16:18">
+      <c r="P74" s="7"/>
+      <c r="Q74" s="7"/>
+      <c r="R74" s="7"/>
+    </row>
+    <row r="75" spans="16:18">
+      <c r="P75" s="7"/>
+      <c r="Q75" s="7"/>
+      <c r="R75" s="7"/>
+    </row>
+    <row r="76" spans="16:18">
+      <c r="P76" s="7"/>
+      <c r="Q76" s="7"/>
+      <c r="R76" s="7"/>
+    </row>
+    <row r="77" spans="16:18">
+      <c r="P77" s="7"/>
+      <c r="Q77" s="7"/>
+      <c r="R77" s="7"/>
+    </row>
+    <row r="78" spans="16:18">
+      <c r="P78" s="7"/>
+      <c r="Q78" s="7"/>
+      <c r="R78" s="7"/>
+    </row>
+    <row r="79" spans="16:18">
+      <c r="P79" s="7"/>
+      <c r="Q79" s="7"/>
+      <c r="R79" s="7"/>
+    </row>
+    <row r="80" spans="16:18">
+      <c r="P80" s="7"/>
+      <c r="Q80" s="7"/>
+      <c r="R80" s="7"/>
+    </row>
+    <row r="81" spans="16:18">
+      <c r="P81" s="7"/>
+      <c r="Q81" s="7"/>
+      <c r="R81" s="7"/>
+    </row>
+    <row r="82" spans="16:18">
+      <c r="P82" s="7"/>
+      <c r="Q82" s="7"/>
+      <c r="R82" s="7"/>
+    </row>
+    <row r="83" spans="16:18">
+      <c r="P83" s="7"/>
+      <c r="Q83" s="7"/>
+      <c r="R83" s="7"/>
+    </row>
+    <row r="84" spans="16:18">
+      <c r="P84" s="7"/>
+      <c r="Q84" s="7"/>
+      <c r="R84" s="7"/>
+    </row>
+    <row r="85" spans="16:18">
+      <c r="P85" s="7"/>
+      <c r="Q85" s="7"/>
+      <c r="R85" s="7"/>
+    </row>
+    <row r="86" spans="16:18">
+      <c r="P86" s="7"/>
+      <c r="Q86" s="7"/>
+      <c r="R86" s="7"/>
+    </row>
+    <row r="87" spans="16:18">
+      <c r="P87" s="7"/>
+      <c r="Q87" s="7"/>
+      <c r="R87" s="7"/>
+    </row>
+    <row r="88" spans="16:18">
+      <c r="P88" s="7"/>
+      <c r="Q88" s="7"/>
+      <c r="R88" s="7"/>
+    </row>
+    <row r="89" spans="16:18">
+      <c r="P89" s="7"/>
+      <c r="Q89" s="7"/>
+      <c r="R89" s="7"/>
+    </row>
+    <row r="90" spans="16:18">
+      <c r="P90" s="7"/>
+      <c r="Q90" s="7"/>
+      <c r="R90" s="7"/>
+    </row>
+    <row r="91" spans="16:18">
+      <c r="P91" s="7"/>
+      <c r="Q91" s="7"/>
+      <c r="R91" s="7"/>
+    </row>
+    <row r="92" spans="16:18">
+      <c r="P92" s="7"/>
+      <c r="Q92" s="7"/>
+      <c r="R92" s="7"/>
+    </row>
+    <row r="93" spans="16:18">
+      <c r="P93" s="7"/>
+      <c r="Q93" s="7"/>
+      <c r="R93" s="7"/>
+    </row>
+    <row r="94" spans="16:18">
+      <c r="P94" s="7"/>
+      <c r="Q94" s="7"/>
+      <c r="R94" s="7"/>
+    </row>
+    <row r="95" spans="16:18">
+      <c r="P95" s="7"/>
+      <c r="Q95" s="7"/>
+      <c r="R95" s="7"/>
+    </row>
+    <row r="96" spans="16:18">
+      <c r="P96" s="7"/>
+      <c r="Q96" s="7"/>
+      <c r="R96" s="7"/>
+    </row>
+    <row r="97" spans="16:18">
+      <c r="P97" s="7"/>
+      <c r="Q97" s="7"/>
+      <c r="R97" s="7"/>
+    </row>
+    <row r="98" spans="16:18">
+      <c r="P98" s="7"/>
+      <c r="Q98" s="7"/>
+      <c r="R98" s="7"/>
+    </row>
+    <row r="99" spans="16:18">
+      <c r="P99" s="7"/>
+      <c r="Q99" s="7"/>
+      <c r="R99" s="7"/>
+    </row>
+    <row r="100" spans="16:18">
+      <c r="P100" s="7"/>
+      <c r="Q100" s="7"/>
+      <c r="R100" s="7"/>
+    </row>
+    <row r="101" spans="16:18">
+      <c r="P101" s="7"/>
+      <c r="Q101" s="7"/>
+      <c r="R101" s="7"/>
+    </row>
+    <row r="102" spans="16:18">
+      <c r="P102" s="7"/>
+      <c r="Q102" s="7"/>
+      <c r="R102" s="7"/>
+    </row>
+    <row r="103" spans="16:18">
+      <c r="P103" s="7"/>
+      <c r="Q103" s="7"/>
+      <c r="R103" s="7"/>
+    </row>
+    <row r="104" spans="16:18">
+      <c r="P104" s="7"/>
+      <c r="Q104" s="7"/>
+      <c r="R104" s="7"/>
+    </row>
+    <row r="105" spans="16:18">
+      <c r="P105" s="7"/>
+      <c r="Q105" s="7"/>
+      <c r="R105" s="7"/>
+    </row>
+    <row r="106" spans="16:18">
+      <c r="P106" s="7"/>
+      <c r="Q106" s="7"/>
+      <c r="R106" s="7"/>
+    </row>
+    <row r="107" spans="16:18">
+      <c r="P107" s="7"/>
+      <c r="Q107" s="7"/>
+      <c r="R107" s="7"/>
+    </row>
+    <row r="108" spans="16:18">
+      <c r="P108" s="7"/>
+      <c r="Q108" s="7"/>
+      <c r="R108" s="7"/>
+    </row>
+    <row r="109" spans="16:18">
+      <c r="P109" s="7"/>
+      <c r="Q109" s="7"/>
+      <c r="R109" s="7"/>
+    </row>
+    <row r="110" spans="16:18">
+      <c r="P110" s="7"/>
+      <c r="Q110" s="7"/>
+      <c r="R110" s="7"/>
+    </row>
+    <row r="111" spans="16:18">
+      <c r="P111" s="7"/>
+      <c r="Q111" s="7"/>
+      <c r="R111" s="7"/>
+    </row>
+    <row r="112" spans="16:18">
+      <c r="P112" s="7"/>
+      <c r="Q112" s="7"/>
+      <c r="R112" s="7"/>
+    </row>
+    <row r="113" spans="16:18">
+      <c r="P113" s="7"/>
+      <c r="Q113" s="7"/>
+      <c r="R113" s="7"/>
+    </row>
+    <row r="114" spans="16:18">
+      <c r="P114" s="7"/>
+      <c r="Q114" s="7"/>
+      <c r="R114" s="7"/>
+    </row>
+    <row r="115" spans="16:18">
+      <c r="P115" s="7"/>
+      <c r="Q115" s="7"/>
+      <c r="R115" s="7"/>
+    </row>
+    <row r="116" spans="16:18">
+      <c r="P116" s="7"/>
+      <c r="Q116" s="7"/>
+      <c r="R116" s="7"/>
+    </row>
+    <row r="117" spans="16:18">
+      <c r="P117" s="7"/>
+      <c r="Q117" s="7"/>
+      <c r="R117" s="7"/>
+    </row>
+    <row r="118" spans="16:18">
+      <c r="P118" s="7"/>
+      <c r="Q118" s="7"/>
+      <c r="R118" s="7"/>
+    </row>
+    <row r="119" spans="16:18">
+      <c r="P119" s="7"/>
+      <c r="Q119" s="7"/>
+      <c r="R119" s="7"/>
+    </row>
+    <row r="120" spans="16:18">
+      <c r="P120" s="7"/>
+      <c r="Q120" s="7"/>
+      <c r="R120" s="7"/>
+    </row>
+    <row r="121" spans="16:18">
+      <c r="P121" s="7"/>
+      <c r="Q121" s="7"/>
+      <c r="R121" s="7"/>
+    </row>
+    <row r="122" spans="16:18">
+      <c r="P122" s="7"/>
+      <c r="Q122" s="7"/>
+      <c r="R122" s="7"/>
+    </row>
+    <row r="123" spans="16:18">
+      <c r="P123" s="7"/>
+      <c r="Q123" s="7"/>
+      <c r="R123" s="7"/>
+    </row>
+    <row r="124" spans="16:18">
+      <c r="P124" s="7"/>
+      <c r="Q124" s="7"/>
+      <c r="R124" s="7"/>
+    </row>
+    <row r="125" spans="16:18">
+      <c r="P125" s="7"/>
+      <c r="Q125" s="7"/>
+      <c r="R125" s="7"/>
+    </row>
+    <row r="126" spans="16:18">
+      <c r="P126" s="7"/>
+      <c r="Q126" s="7"/>
+      <c r="R126" s="7"/>
+    </row>
+    <row r="127" spans="16:18">
+      <c r="P127" s="7"/>
+      <c r="Q127" s="7"/>
+      <c r="R127" s="7"/>
+    </row>
+    <row r="128" spans="16:18">
+      <c r="P128" s="7"/>
+      <c r="Q128" s="7"/>
+      <c r="R128" s="7"/>
+    </row>
+    <row r="129" spans="16:18">
+      <c r="P129" s="7"/>
+      <c r="Q129" s="7"/>
+      <c r="R129" s="7"/>
+    </row>
+    <row r="130" spans="16:18">
+      <c r="P130" s="7"/>
+      <c r="Q130" s="7"/>
+      <c r="R130" s="7"/>
+    </row>
+    <row r="131" spans="16:18">
+      <c r="P131" s="7"/>
+      <c r="Q131" s="7"/>
+      <c r="R131" s="7"/>
+    </row>
+    <row r="132" spans="16:18">
+      <c r="P132" s="7"/>
+      <c r="Q132" s="7"/>
+      <c r="R132" s="7"/>
+    </row>
+    <row r="133" spans="16:18">
+      <c r="P133" s="7"/>
+      <c r="Q133" s="7"/>
+      <c r="R133" s="7"/>
+    </row>
+    <row r="134" spans="16:18">
+      <c r="P134" s="7"/>
+      <c r="Q134" s="7"/>
+      <c r="R134" s="7"/>
+    </row>
+    <row r="135" spans="16:18">
+      <c r="P135" s="7"/>
+      <c r="Q135" s="7"/>
+      <c r="R135" s="7"/>
+    </row>
+    <row r="136" spans="16:18">
+      <c r="P136" s="7"/>
+      <c r="Q136" s="7"/>
+      <c r="R136" s="7"/>
+    </row>
+    <row r="137" spans="16:18">
+      <c r="P137" s="7"/>
+      <c r="Q137" s="7"/>
+      <c r="R137" s="7"/>
+    </row>
+    <row r="138" spans="16:18">
+      <c r="P138" s="7"/>
+      <c r="Q138" s="7"/>
+      <c r="R138" s="7"/>
+    </row>
+    <row r="139" spans="16:18">
+      <c r="P139" s="7"/>
+      <c r="Q139" s="7"/>
+      <c r="R139" s="7"/>
+    </row>
+    <row r="140" spans="16:18">
+      <c r="P140" s="7"/>
+      <c r="Q140" s="7"/>
+      <c r="R140" s="7"/>
+    </row>
+    <row r="141" spans="16:18">
+      <c r="P141" s="7"/>
+      <c r="Q141" s="7"/>
+      <c r="R141" s="7"/>
+    </row>
+    <row r="142" spans="16:18">
+      <c r="P142" s="7"/>
+      <c r="Q142" s="7"/>
+      <c r="R142" s="7"/>
+    </row>
+    <row r="143" spans="16:18">
+      <c r="P143" s="7"/>
+      <c r="Q143" s="7"/>
+      <c r="R143" s="7"/>
+    </row>
+    <row r="144" spans="16:18">
+      <c r="P144" s="7"/>
+      <c r="Q144" s="7"/>
+      <c r="R144" s="7"/>
+    </row>
+    <row r="145" spans="16:18">
+      <c r="P145" s="7"/>
+      <c r="Q145" s="7"/>
+      <c r="R145" s="7"/>
+    </row>
+    <row r="146" spans="16:18">
+      <c r="P146" s="7"/>
+      <c r="Q146" s="7"/>
+      <c r="R146" s="7"/>
+    </row>
+    <row r="147" spans="16:18">
+      <c r="P147" s="7"/>
+      <c r="Q147" s="7"/>
+      <c r="R147" s="7"/>
+    </row>
+    <row r="148" spans="16:18">
+      <c r="P148" s="7"/>
+      <c r="Q148" s="7"/>
+      <c r="R148" s="7"/>
+    </row>
+    <row r="149" spans="16:18">
+      <c r="P149" s="7"/>
+      <c r="Q149" s="7"/>
+      <c r="R149" s="7"/>
+    </row>
+    <row r="150" spans="16:18">
+      <c r="P150" s="7"/>
+      <c r="Q150" s="7"/>
+      <c r="R150" s="7"/>
+    </row>
+    <row r="151" spans="16:18">
+      <c r="P151" s="7"/>
+      <c r="Q151" s="7"/>
+      <c r="R151" s="7"/>
+    </row>
+    <row r="152" spans="16:18">
+      <c r="P152" s="7"/>
+      <c r="Q152" s="7"/>
+      <c r="R152" s="7"/>
+    </row>
+    <row r="153" spans="16:18">
+      <c r="P153" s="7"/>
+      <c r="Q153" s="7"/>
+      <c r="R153" s="7"/>
+    </row>
+    <row r="154" spans="16:18">
+      <c r="P154" s="7"/>
+      <c r="Q154" s="7"/>
+      <c r="R154" s="7"/>
+    </row>
+    <row r="155" spans="16:18">
+      <c r="P155" s="7"/>
+      <c r="Q155" s="7"/>
+      <c r="R155" s="7"/>
+    </row>
+    <row r="156" spans="16:18">
+      <c r="P156" s="7"/>
+      <c r="Q156" s="7"/>
+      <c r="R156" s="7"/>
+    </row>
+    <row r="157" spans="16:18">
+      <c r="P157" s="7"/>
+      <c r="Q157" s="7"/>
+      <c r="R157" s="7"/>
+    </row>
+    <row r="158" spans="16:18">
+      <c r="P158" s="7"/>
+      <c r="Q158" s="7"/>
+      <c r="R158" s="7"/>
+    </row>
+    <row r="159" spans="16:18">
+      <c r="P159" s="7"/>
+      <c r="Q159" s="7"/>
+      <c r="R159" s="7"/>
+    </row>
+    <row r="160" spans="16:18">
+      <c r="P160" s="7"/>
+      <c r="Q160" s="7"/>
+      <c r="R160" s="7"/>
+    </row>
+    <row r="161" spans="16:18">
+      <c r="P161" s="7"/>
+      <c r="Q161" s="7"/>
+      <c r="R161" s="7"/>
+    </row>
+    <row r="162" spans="16:18">
+      <c r="P162" s="7"/>
+      <c r="Q162" s="7"/>
+      <c r="R162" s="7"/>
+    </row>
+    <row r="163" spans="16:18">
+      <c r="P163" s="7"/>
+      <c r="Q163" s="7"/>
+      <c r="R163" s="7"/>
+    </row>
+    <row r="164" spans="16:18">
+      <c r="P164" s="7"/>
+      <c r="Q164" s="7"/>
+      <c r="R164" s="7"/>
+    </row>
+    <row r="165" spans="16:18">
+      <c r="P165" s="7"/>
+      <c r="Q165" s="7"/>
+      <c r="R165" s="7"/>
+    </row>
+    <row r="166" spans="16:18">
+      <c r="P166" s="7"/>
+      <c r="Q166" s="7"/>
+      <c r="R166" s="7"/>
+    </row>
+    <row r="167" spans="16:18">
+      <c r="P167" s="7"/>
+      <c r="Q167" s="7"/>
+      <c r="R167" s="7"/>
+    </row>
+    <row r="168" spans="16:18">
+      <c r="P168" s="7"/>
+      <c r="Q168" s="7"/>
+      <c r="R168" s="7"/>
+    </row>
+    <row r="169" spans="16:18">
+      <c r="P169" s="7"/>
+      <c r="Q169" s="7"/>
+      <c r="R169" s="7"/>
+    </row>
+    <row r="170" spans="16:18">
+      <c r="P170" s="7"/>
+      <c r="Q170" s="7"/>
+      <c r="R170" s="7"/>
+    </row>
+    <row r="171" spans="16:18">
+      <c r="P171" s="7"/>
+      <c r="Q171" s="7"/>
+      <c r="R171" s="7"/>
+    </row>
+    <row r="172" spans="16:18">
+      <c r="P172" s="7"/>
+      <c r="Q172" s="7"/>
+      <c r="R172" s="7"/>
+    </row>
+    <row r="173" spans="16:18">
+      <c r="P173" s="7"/>
+      <c r="Q173" s="7"/>
+      <c r="R173" s="7"/>
+    </row>
+    <row r="174" spans="16:18">
+      <c r="P174" s="7"/>
+      <c r="Q174" s="7"/>
+      <c r="R174" s="7"/>
+    </row>
+    <row r="175" spans="16:18">
+      <c r="P175" s="7"/>
+      <c r="Q175" s="7"/>
+      <c r="R175" s="7"/>
+    </row>
+    <row r="176" spans="16:18">
+      <c r="P176" s="7"/>
+      <c r="Q176" s="7"/>
+      <c r="R176" s="7"/>
+    </row>
+    <row r="177" spans="16:18">
+      <c r="P177" s="7"/>
+      <c r="Q177" s="7"/>
+      <c r="R177" s="7"/>
+    </row>
+    <row r="178" spans="16:18">
+      <c r="P178" s="7"/>
+      <c r="Q178" s="7"/>
+      <c r="R178" s="7"/>
+    </row>
+    <row r="179" spans="16:18">
+      <c r="P179" s="7"/>
+      <c r="Q179" s="7"/>
+      <c r="R179" s="7"/>
+    </row>
+    <row r="180" spans="16:18">
+      <c r="P180" s="7"/>
+      <c r="Q180" s="7"/>
+      <c r="R180" s="7"/>
+    </row>
+    <row r="181" spans="16:18">
+      <c r="P181" s="7"/>
+      <c r="Q181" s="7"/>
+      <c r="R181" s="7"/>
+    </row>
+    <row r="182" spans="16:18">
+      <c r="P182" s="7"/>
+      <c r="Q182" s="7"/>
+      <c r="R182" s="7"/>
+    </row>
+    <row r="183" spans="16:18">
+      <c r="P183" s="7"/>
+      <c r="Q183" s="7"/>
+      <c r="R183" s="7"/>
+    </row>
+    <row r="184" spans="16:18">
+      <c r="P184" s="7"/>
+      <c r="Q184" s="7"/>
+      <c r="R184" s="7"/>
+    </row>
+    <row r="185" spans="16:18">
+      <c r="P185" s="7"/>
+      <c r="Q185" s="7"/>
+      <c r="R185" s="7"/>
+    </row>
+    <row r="186" spans="16:18">
+      <c r="P186" s="7"/>
+      <c r="Q186" s="7"/>
+      <c r="R186" s="7"/>
+    </row>
+    <row r="187" spans="16:18">
+      <c r="P187" s="7"/>
+      <c r="Q187" s="7"/>
+      <c r="R187" s="7"/>
+    </row>
+    <row r="188" spans="16:18">
+      <c r="P188" s="7"/>
+      <c r="Q188" s="7"/>
+      <c r="R188" s="7"/>
+    </row>
+    <row r="189" spans="16:18">
+      <c r="P189" s="7"/>
+      <c r="Q189" s="7"/>
+      <c r="R189" s="7"/>
+    </row>
+    <row r="190" spans="16:18">
+      <c r="P190" s="7"/>
+      <c r="Q190" s="7"/>
+      <c r="R190" s="7"/>
+    </row>
+    <row r="191" spans="16:18">
+      <c r="P191" s="7"/>
+      <c r="Q191" s="7"/>
+      <c r="R191" s="7"/>
+    </row>
+    <row r="192" spans="16:18">
+      <c r="P192" s="7"/>
+      <c r="Q192" s="7"/>
+      <c r="R192" s="7"/>
+    </row>
+    <row r="193" spans="16:18">
+      <c r="P193" s="7"/>
+      <c r="Q193" s="7"/>
+      <c r="R193" s="7"/>
+    </row>
+    <row r="194" spans="16:18">
+      <c r="P194" s="7"/>
+      <c r="Q194" s="7"/>
+      <c r="R194" s="7"/>
+    </row>
+    <row r="195" spans="16:18">
+      <c r="P195" s="7"/>
+      <c r="Q195" s="7"/>
+      <c r="R195" s="7"/>
+    </row>
+    <row r="196" spans="16:18">
+      <c r="P196" s="7"/>
+      <c r="Q196" s="7"/>
+      <c r="R196" s="7"/>
+    </row>
+    <row r="197" spans="16:18">
+      <c r="P197" s="7"/>
+      <c r="Q197" s="7"/>
+      <c r="R197" s="7"/>
+    </row>
+    <row r="198" spans="16:18">
+      <c r="P198" s="7"/>
+      <c r="Q198" s="7"/>
+      <c r="R198" s="7"/>
+    </row>
+    <row r="199" spans="16:18">
+      <c r="P199" s="7"/>
+      <c r="Q199" s="7"/>
+      <c r="R199" s="7"/>
+    </row>
+    <row r="200" spans="16:18">
+      <c r="P200" s="7"/>
+      <c r="Q200" s="7"/>
+      <c r="R200" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
